--- a/research/traditional_assets/database/data/france/france_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/france/france_chemical_diversified.xlsx
@@ -588,109 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.253</v>
+        <v>0.794</v>
+      </c>
+      <c r="E2">
+        <v>0.412</v>
       </c>
       <c r="G2">
-        <v>-103</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-103</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-1610</v>
+        <v>-0.3411764705882353</v>
       </c>
       <c r="J2">
-        <v>-1610</v>
+        <v>-0.3411764705882353</v>
       </c>
       <c r="K2">
-        <v>-0.586</v>
+        <v>1.36</v>
       </c>
       <c r="L2">
-        <v>-586</v>
+        <v>16</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3248</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04906344410876132</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.2388235294117647</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.3248</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04906344410876132</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.2388235294117647</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.504</v>
+        <v>0.055</v>
       </c>
       <c r="V2">
-        <v>0.06307884856070088</v>
+        <v>0.008308157099697885</v>
       </c>
       <c r="W2">
-        <v>-0.04156028368794326</v>
+        <v>0.1079365079365079</v>
       </c>
       <c r="X2">
-        <v>0.1031932198217237</v>
+        <v>0.08418129577395657</v>
       </c>
       <c r="Y2">
-        <v>-0.144753503509667</v>
+        <v>0.02375521216255137</v>
       </c>
       <c r="Z2">
-        <v>7.092701610043265e-05</v>
+        <v>0.006839945280437757</v>
       </c>
       <c r="AA2">
-        <v>-0.1141924959216966</v>
+        <v>-0.002333628389796411</v>
       </c>
       <c r="AB2">
-        <v>0.1027690319070085</v>
+        <v>0.08401381002355</v>
       </c>
       <c r="AC2">
-        <v>-0.2169615278287051</v>
+        <v>-0.08634743841334641</v>
       </c>
       <c r="AD2">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
       <c r="AG2">
-        <v>-0.45</v>
+        <v>-0.031</v>
       </c>
       <c r="AH2">
-        <v>0.006713078070611635</v>
+        <v>0.003612281757977122</v>
       </c>
       <c r="AI2">
-        <v>0.004517316379454576</v>
+        <v>0.001814882032667877</v>
       </c>
       <c r="AJ2">
-        <v>-0.0596816976127321</v>
+        <v>-0.004704811048717559</v>
       </c>
       <c r="AK2">
-        <v>-0.03930131004366812</v>
+        <v>-0.002354013212848356</v>
       </c>
       <c r="AL2">
-        <v>0.232</v>
+        <v>1.47</v>
       </c>
       <c r="AM2">
-        <v>-0.481</v>
+        <v>0.848</v>
       </c>
       <c r="AO2">
-        <v>-6.939655172413794</v>
+        <v>-0.01972789115646259</v>
       </c>
       <c r="AQ2">
-        <v>3.347193347193348</v>
+        <v>-0.03419811320754717</v>
       </c>
     </row>
     <row r="3">
@@ -710,109 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.253</v>
+        <v>0.794</v>
+      </c>
+      <c r="E3">
+        <v>0.412</v>
       </c>
       <c r="G3">
-        <v>-103</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-103</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-1610</v>
+        <v>-0.3411764705882353</v>
       </c>
       <c r="J3">
-        <v>-1610</v>
+        <v>-0.3411764705882353</v>
       </c>
       <c r="K3">
-        <v>-0.586</v>
+        <v>1.36</v>
       </c>
       <c r="L3">
-        <v>-586</v>
+        <v>16</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.3248</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04906344410876132</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.2388235294117647</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.3248</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04906344410876132</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.2388235294117647</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.504</v>
+        <v>0.055</v>
       </c>
       <c r="V3">
-        <v>0.06307884856070088</v>
+        <v>0.008308157099697885</v>
       </c>
       <c r="W3">
-        <v>-0.04156028368794326</v>
+        <v>0.1079365079365079</v>
       </c>
       <c r="X3">
-        <v>0.1031932198217237</v>
+        <v>0.08418129577395657</v>
       </c>
       <c r="Y3">
-        <v>-0.144753503509667</v>
+        <v>0.02375521216255137</v>
       </c>
       <c r="Z3">
-        <v>7.092701610043265e-05</v>
+        <v>0.006839945280437757</v>
       </c>
       <c r="AA3">
-        <v>-0.1141924959216966</v>
+        <v>-0.002333628389796411</v>
       </c>
       <c r="AB3">
-        <v>0.1027690319070085</v>
+        <v>0.08401381002355</v>
       </c>
       <c r="AC3">
-        <v>-0.2169615278287051</v>
+        <v>-0.08634743841334641</v>
       </c>
       <c r="AD3">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
       <c r="AG3">
-        <v>-0.45</v>
+        <v>-0.031</v>
       </c>
       <c r="AH3">
-        <v>0.006713078070611635</v>
+        <v>0.003612281757977122</v>
       </c>
       <c r="AI3">
-        <v>0.004517316379454576</v>
+        <v>0.001814882032667877</v>
       </c>
       <c r="AJ3">
-        <v>-0.0596816976127321</v>
+        <v>-0.004704811048717559</v>
       </c>
       <c r="AK3">
-        <v>-0.03930131004366812</v>
+        <v>-0.002354013212848356</v>
       </c>
       <c r="AL3">
-        <v>0.232</v>
+        <v>1.47</v>
       </c>
       <c r="AM3">
-        <v>-0.481</v>
+        <v>0.848</v>
       </c>
       <c r="AO3">
-        <v>-6.939655172413794</v>
+        <v>-0.01972789115646259</v>
       </c>
       <c r="AQ3">
-        <v>3.347193347193348</v>
+        <v>-0.03419811320754717</v>
       </c>
     </row>
   </sheetData>
